--- a/data/trucks.xlsx
+++ b/data/trucks.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sreek\global-pacific-truck-search\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85BDAEEC-1DBE-40FA-A1EE-DF0539A12FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95B5951D-B0EA-4986-8693-05742C4D9901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{0BA495CA-0163-448B-A209-738BC85836F3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0BA495CA-0163-448B-A209-738BC85836F3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10127" uniqueCount="2274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10127" uniqueCount="2275">
   <si>
     <t>DOC RCVD
 DATE</t>
@@ -6857,6 +6857,9 @@
   </si>
   <si>
     <t>TRAILER NO</t>
+  </si>
+  <si>
+    <t>ALAM jaz</t>
   </si>
 </sst>
 </file>
@@ -7855,7 +7858,7 @@
         <v>12</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>13</v>
+        <v>2274</v>
       </c>
       <c r="I2" s="11" t="s">
         <v>14</v>
